--- a/data/nzd0064/nzd0064.xlsx
+++ b/data/nzd0064/nzd0064.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N356"/>
+  <dimension ref="A1:N357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17526,6 +17526,54 @@
         <v>392.24</v>
       </c>
       <c r="N356" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>381.99</v>
+      </c>
+      <c r="C357" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="D357" t="n">
+        <v>385.91</v>
+      </c>
+      <c r="E357" t="n">
+        <v>383.46</v>
+      </c>
+      <c r="F357" t="n">
+        <v>381.49</v>
+      </c>
+      <c r="G357" t="n">
+        <v>382.34</v>
+      </c>
+      <c r="H357" t="n">
+        <v>375.92</v>
+      </c>
+      <c r="I357" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="J357" t="n">
+        <v>382.51</v>
+      </c>
+      <c r="K357" t="n">
+        <v>376.99</v>
+      </c>
+      <c r="L357" t="n">
+        <v>388.15</v>
+      </c>
+      <c r="M357" t="n">
+        <v>392.04</v>
+      </c>
+      <c r="N357" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17542,7 +17590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B363"/>
+  <dimension ref="A1:B364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21175,6 +21223,16 @@
       </c>
       <c r="B363" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -21343,28 +21401,28 @@
         <v>0.0688</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.002521614375690222</v>
+        <v>-0.003252644102235886</v>
       </c>
       <c r="J2" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K2" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L2" t="n">
-        <v>3.300638475656203e-05</v>
+        <v>5.524233948805968e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.294479616629662</v>
+        <v>2.291430372698336</v>
       </c>
       <c r="N2" t="n">
-        <v>10.02888011924683</v>
+        <v>10.00477093753382</v>
       </c>
       <c r="O2" t="n">
-        <v>3.166840715799712</v>
+        <v>3.163031921674806</v>
       </c>
       <c r="P2" t="n">
-        <v>383.3039535948602</v>
+        <v>383.3117463469194</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21425,28 +21483,28 @@
         <v>0.1268</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03357100015452713</v>
+        <v>0.03180447776089216</v>
       </c>
       <c r="J3" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K3" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007590336611706494</v>
+        <v>0.006838031887740792</v>
       </c>
       <c r="M3" t="n">
-        <v>2.019520129338189</v>
+        <v>2.022550945606098</v>
       </c>
       <c r="N3" t="n">
-        <v>7.777623479091565</v>
+        <v>7.781812009317514</v>
       </c>
       <c r="O3" t="n">
-        <v>2.788839091645763</v>
+        <v>2.789589935692613</v>
       </c>
       <c r="P3" t="n">
-        <v>382.7210490331173</v>
+        <v>382.7396480218809</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21507,28 +21565,28 @@
         <v>0.1164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02591504615027393</v>
+        <v>0.02465199992579119</v>
       </c>
       <c r="J4" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004316845088978338</v>
+        <v>0.003926243469036028</v>
       </c>
       <c r="M4" t="n">
-        <v>2.126991627500715</v>
+        <v>2.127406328139825</v>
       </c>
       <c r="N4" t="n">
-        <v>8.176116577181281</v>
+        <v>8.166459738551392</v>
       </c>
       <c r="O4" t="n">
-        <v>2.859390945145711</v>
+        <v>2.857701828139422</v>
       </c>
       <c r="P4" t="n">
-        <v>387.4205970857263</v>
+        <v>387.4338951806849</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21589,28 +21647,28 @@
         <v>0.1182</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07234183874184388</v>
+        <v>-0.07206701934669903</v>
       </c>
       <c r="J5" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K5" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0276661131513033</v>
+        <v>0.02762985386692651</v>
       </c>
       <c r="M5" t="n">
-        <v>2.434485208657045</v>
+        <v>2.42891227878863</v>
       </c>
       <c r="N5" t="n">
-        <v>9.708111722189397</v>
+        <v>9.681471871119323</v>
       </c>
       <c r="O5" t="n">
-        <v>3.115784286851289</v>
+        <v>3.111506366877517</v>
       </c>
       <c r="P5" t="n">
-        <v>384.8872546682302</v>
+        <v>384.8843612076882</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21671,28 +21729,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03405362970778087</v>
+        <v>-0.03474589555239001</v>
       </c>
       <c r="J6" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K6" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007787436441834106</v>
+        <v>0.008151556826892614</v>
       </c>
       <c r="M6" t="n">
-        <v>2.103094572294824</v>
+        <v>2.10056346556902</v>
       </c>
       <c r="N6" t="n">
-        <v>7.798757776227148</v>
+        <v>7.780849479508331</v>
       </c>
       <c r="O6" t="n">
-        <v>2.792625606168351</v>
+        <v>2.789417408619286</v>
       </c>
       <c r="P6" t="n">
-        <v>383.5885747974319</v>
+        <v>383.5958633801931</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21753,28 +21811,28 @@
         <v>0.1432</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07067547410831727</v>
+        <v>0.06955611595341081</v>
       </c>
       <c r="J7" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K7" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02574411660774567</v>
+        <v>0.02508405398429647</v>
       </c>
       <c r="M7" t="n">
-        <v>2.519540124199518</v>
+        <v>2.517743333455608</v>
       </c>
       <c r="N7" t="n">
-        <v>9.9774810281243</v>
+        <v>9.959908108569614</v>
       </c>
       <c r="O7" t="n">
-        <v>3.158715091318668</v>
+        <v>3.155932209121358</v>
       </c>
       <c r="P7" t="n">
-        <v>382.4220395604136</v>
+        <v>382.4338248227011</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -21835,28 +21893,28 @@
         <v>0.1037</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01644083710690755</v>
+        <v>0.01450508555767924</v>
       </c>
       <c r="J8" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K8" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001610058453192176</v>
+        <v>0.001257187438967855</v>
       </c>
       <c r="M8" t="n">
-        <v>2.290542285965536</v>
+        <v>2.291965718001931</v>
       </c>
       <c r="N8" t="n">
-        <v>8.846975261591886</v>
+        <v>8.853387279402909</v>
       </c>
       <c r="O8" t="n">
-        <v>2.974386535336638</v>
+        <v>2.975464212421805</v>
       </c>
       <c r="P8" t="n">
-        <v>378.8349907859196</v>
+        <v>378.8553715189593</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21917,28 +21975,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04278094788091525</v>
+        <v>0.04027692034242438</v>
       </c>
       <c r="J9" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K9" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009117191136020941</v>
+        <v>0.008100318067553847</v>
       </c>
       <c r="M9" t="n">
-        <v>2.523183903870841</v>
+        <v>2.527742207356258</v>
       </c>
       <c r="N9" t="n">
-        <v>10.49906069129389</v>
+        <v>10.52188206750469</v>
       </c>
       <c r="O9" t="n">
-        <v>3.240225407482308</v>
+        <v>3.243745068205067</v>
       </c>
       <c r="P9" t="n">
-        <v>371.6065491199097</v>
+        <v>371.6329129974467</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -21999,28 +22057,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01784569716223241</v>
+        <v>0.01627616293429382</v>
       </c>
       <c r="J10" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K10" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002242315379254012</v>
+        <v>0.001872612851670064</v>
       </c>
       <c r="M10" t="n">
-        <v>2.121383151152539</v>
+        <v>2.123384125439204</v>
       </c>
       <c r="N10" t="n">
-        <v>7.479693980694951</v>
+        <v>7.479236546542082</v>
       </c>
       <c r="O10" t="n">
-        <v>2.734902919793489</v>
+        <v>2.734819289558651</v>
       </c>
       <c r="P10" t="n">
-        <v>384.7554571030958</v>
+        <v>384.7719820843668</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22081,28 +22139,28 @@
         <v>0.1052</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1013768607057109</v>
+        <v>0.09969911286273123</v>
       </c>
       <c r="J11" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K11" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04262999593471994</v>
+        <v>0.04146284034552872</v>
       </c>
       <c r="M11" t="n">
-        <v>2.630587744762237</v>
+        <v>2.629356265041702</v>
       </c>
       <c r="N11" t="n">
-        <v>12.18233697524766</v>
+        <v>12.17160166975072</v>
       </c>
       <c r="O11" t="n">
-        <v>3.49032046884633</v>
+        <v>3.488782261728399</v>
       </c>
       <c r="P11" t="n">
-        <v>377.2344716179941</v>
+        <v>377.252135935974</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22163,28 +22221,28 @@
         <v>0.056</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01949144570176049</v>
+        <v>0.01719176608661823</v>
       </c>
       <c r="J12" t="n">
+        <v>356</v>
+      </c>
+      <c r="K12" t="n">
         <v>355</v>
       </c>
-      <c r="K12" t="n">
-        <v>354</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.0018598128489965</v>
+        <v>0.001450684628675147</v>
       </c>
       <c r="M12" t="n">
-        <v>2.615390848778528</v>
+        <v>2.619298637709231</v>
       </c>
       <c r="N12" t="n">
-        <v>10.71130747634712</v>
+        <v>10.72498799885564</v>
       </c>
       <c r="O12" t="n">
-        <v>3.272813388561457</v>
+        <v>3.274902746472885</v>
       </c>
       <c r="P12" t="n">
-        <v>391.6057108989891</v>
+        <v>391.6300187881938</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22245,28 +22303,28 @@
         <v>0.0634</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1043633897089966</v>
+        <v>-0.1063126576626575</v>
       </c>
       <c r="J13" t="n">
+        <v>356</v>
+      </c>
+      <c r="K13" t="n">
         <v>355</v>
       </c>
-      <c r="K13" t="n">
-        <v>354</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.05555877507207374</v>
+        <v>0.05770106465668479</v>
       </c>
       <c r="M13" t="n">
-        <v>2.522788140640007</v>
+        <v>2.524496660229818</v>
       </c>
       <c r="N13" t="n">
-        <v>9.726368295900299</v>
+        <v>9.730477281809806</v>
       </c>
       <c r="O13" t="n">
-        <v>3.118712602324924</v>
+        <v>3.11937129592003</v>
       </c>
       <c r="P13" t="n">
-        <v>398.1456352200317</v>
+        <v>398.1662392159692</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22308,7 +22366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N356"/>
+  <dimension ref="A1:N357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47919,6 +47977,78 @@
         </is>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-35.257125735262164,174.13145858366914</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-35.257768863490476,174.1317446524764</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-35.25828850590287,174.13230104165487</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-35.258768432062915,174.1329345557069</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-35.25921165453717,174.13362739357908</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-35.25957369098263,174.13437449761224</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-35.25988979508852,174.13516022797458</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-35.26015849236876,174.13599575182403</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-35.26032246465447,174.13686354677623</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-35.26052970672618,174.13770611951915</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-35.26060379512569,174.1386183682203</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-35.26081805410541,174.13948674069837</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0064/nzd0064.xlsx
+++ b/data/nzd0064/nzd0064.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N357"/>
+  <dimension ref="A1:N358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17574,6 +17574,54 @@
         <v>392.04</v>
       </c>
       <c r="N357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>382.29</v>
+      </c>
+      <c r="C358" t="n">
+        <v>380.28</v>
+      </c>
+      <c r="D358" t="n">
+        <v>385.43</v>
+      </c>
+      <c r="E358" t="n">
+        <v>382.28</v>
+      </c>
+      <c r="F358" t="n">
+        <v>379.7</v>
+      </c>
+      <c r="G358" t="n">
+        <v>382.8</v>
+      </c>
+      <c r="H358" t="n">
+        <v>375.2</v>
+      </c>
+      <c r="I358" t="n">
+        <v>369.28</v>
+      </c>
+      <c r="J358" t="n">
+        <v>382</v>
+      </c>
+      <c r="K358" t="n">
+        <v>377.01</v>
+      </c>
+      <c r="L358" t="n">
+        <v>387.8</v>
+      </c>
+      <c r="M358" t="n">
+        <v>392.08</v>
+      </c>
+      <c r="N358" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17590,7 +17638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B364"/>
+  <dimension ref="A1:B365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21233,6 +21281,16 @@
       </c>
       <c r="B364" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -21401,28 +21459,28 @@
         <v>0.0688</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.003252644102235886</v>
+        <v>-0.003799454096751423</v>
       </c>
       <c r="J2" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L2" t="n">
-        <v>5.524233948805968e-05</v>
+        <v>7.583951039091819e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.291430372698336</v>
+        <v>2.287536598383334</v>
       </c>
       <c r="N2" t="n">
-        <v>10.00477093753382</v>
+        <v>9.978879002585526</v>
       </c>
       <c r="O2" t="n">
-        <v>3.163031921674806</v>
+        <v>3.158936372038146</v>
       </c>
       <c r="P2" t="n">
-        <v>383.3117463469194</v>
+        <v>383.3175967073383</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21483,28 +21541,28 @@
         <v>0.1268</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03180447776089216</v>
+        <v>0.02990250498461781</v>
       </c>
       <c r="J3" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K3" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006838031887740792</v>
+        <v>0.006064327258981095</v>
       </c>
       <c r="M3" t="n">
-        <v>2.022550945606098</v>
+        <v>2.026155429966222</v>
       </c>
       <c r="N3" t="n">
-        <v>7.781812009317514</v>
+        <v>7.790179808126085</v>
       </c>
       <c r="O3" t="n">
-        <v>2.789589935692613</v>
+        <v>2.791089358678092</v>
       </c>
       <c r="P3" t="n">
-        <v>382.7396480218809</v>
+        <v>382.7597469232269</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21565,28 +21623,28 @@
         <v>0.1164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02465199992579119</v>
+        <v>0.02311986269946526</v>
       </c>
       <c r="J4" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K4" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003926243469036028</v>
+        <v>0.003468645249913194</v>
       </c>
       <c r="M4" t="n">
-        <v>2.127406328139825</v>
+        <v>2.129125583650952</v>
       </c>
       <c r="N4" t="n">
-        <v>8.166459738551392</v>
+        <v>8.163159357508325</v>
       </c>
       <c r="O4" t="n">
-        <v>2.857701828139422</v>
+        <v>2.857124316075226</v>
       </c>
       <c r="P4" t="n">
-        <v>387.4338951806849</v>
+        <v>387.4500858829624</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21647,28 +21705,28 @@
         <v>0.1182</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07206701934669903</v>
+        <v>-0.07247215127995721</v>
       </c>
       <c r="J5" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K5" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02762985386692651</v>
+        <v>0.02810185677084787</v>
       </c>
       <c r="M5" t="n">
-        <v>2.42891227878863</v>
+        <v>2.424161687131467</v>
       </c>
       <c r="N5" t="n">
-        <v>9.681471871119323</v>
+        <v>9.655721564282736</v>
       </c>
       <c r="O5" t="n">
-        <v>3.111506366877517</v>
+        <v>3.107365695292837</v>
       </c>
       <c r="P5" t="n">
-        <v>384.8843612076882</v>
+        <v>384.8886423976508</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21729,28 +21787,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03474589555239001</v>
+        <v>-0.03646299029492616</v>
       </c>
       <c r="J6" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K6" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008151556826892614</v>
+        <v>0.008998144175488387</v>
       </c>
       <c r="M6" t="n">
-        <v>2.10056346556902</v>
+        <v>2.103006408447279</v>
       </c>
       <c r="N6" t="n">
-        <v>7.780849479508331</v>
+        <v>7.783640603326271</v>
       </c>
       <c r="O6" t="n">
-        <v>2.789417408619286</v>
+        <v>2.789917669632255</v>
       </c>
       <c r="P6" t="n">
-        <v>383.5958633801931</v>
+        <v>383.6140086019662</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21811,28 +21869,28 @@
         <v>0.1432</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06955611595341081</v>
+        <v>0.06871008939515946</v>
       </c>
       <c r="J7" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K7" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02508405398429647</v>
+        <v>0.02463025877187919</v>
       </c>
       <c r="M7" t="n">
-        <v>2.517743333455608</v>
+        <v>2.514673296624768</v>
       </c>
       <c r="N7" t="n">
-        <v>9.959908108569614</v>
+        <v>9.937977789427306</v>
       </c>
       <c r="O7" t="n">
-        <v>3.155932209121358</v>
+        <v>3.152455834651345</v>
       </c>
       <c r="P7" t="n">
-        <v>382.4338248227011</v>
+        <v>382.4427651211862</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -21893,28 +21951,28 @@
         <v>0.1037</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01450508555767924</v>
+        <v>0.01217302430484212</v>
       </c>
       <c r="J8" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K8" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001257187438967855</v>
+        <v>0.0008868535906283448</v>
       </c>
       <c r="M8" t="n">
-        <v>2.291965718001931</v>
+        <v>2.295079556413471</v>
       </c>
       <c r="N8" t="n">
-        <v>8.853387279402909</v>
+        <v>8.873938488068022</v>
       </c>
       <c r="O8" t="n">
-        <v>2.975464212421805</v>
+        <v>2.978915656420642</v>
       </c>
       <c r="P8" t="n">
-        <v>378.8553715189593</v>
+        <v>378.8800153359678</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21975,28 +22033,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04027692034242438</v>
+        <v>0.03830666279774955</v>
       </c>
       <c r="J9" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K9" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008100318067553847</v>
+        <v>0.007356741902165509</v>
       </c>
       <c r="M9" t="n">
-        <v>2.527742207356258</v>
+        <v>2.529815598208961</v>
       </c>
       <c r="N9" t="n">
-        <v>10.52188206750469</v>
+        <v>10.52477949688652</v>
       </c>
       <c r="O9" t="n">
-        <v>3.243745068205067</v>
+        <v>3.244191655387598</v>
       </c>
       <c r="P9" t="n">
-        <v>371.6329129974467</v>
+        <v>371.6537334910472</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22057,28 +22115,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01627616293429382</v>
+        <v>0.01442681245049056</v>
       </c>
       <c r="J10" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K10" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001872612851670064</v>
+        <v>0.001475569230383389</v>
       </c>
       <c r="M10" t="n">
-        <v>2.123384125439204</v>
+        <v>2.126781710553783</v>
       </c>
       <c r="N10" t="n">
-        <v>7.479236546542082</v>
+        <v>7.486805790767458</v>
       </c>
       <c r="O10" t="n">
-        <v>2.734819289558651</v>
+        <v>2.73620280512382</v>
       </c>
       <c r="P10" t="n">
-        <v>384.7719820843668</v>
+        <v>384.791524905059</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22139,28 +22197,28 @@
         <v>0.1052</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09969911286273123</v>
+        <v>0.09804174168260034</v>
       </c>
       <c r="J11" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K11" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04146284034552872</v>
+        <v>0.04032323564911677</v>
       </c>
       <c r="M11" t="n">
-        <v>2.629356265041702</v>
+        <v>2.627996570449004</v>
       </c>
       <c r="N11" t="n">
-        <v>12.17160166975072</v>
+        <v>12.16041320789328</v>
       </c>
       <c r="O11" t="n">
-        <v>3.488782261728399</v>
+        <v>3.487178402074274</v>
       </c>
       <c r="P11" t="n">
-        <v>377.252135935974</v>
+        <v>377.2696500351551</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22221,28 +22279,28 @@
         <v>0.056</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01719176608661823</v>
+        <v>0.01470863123172406</v>
       </c>
       <c r="J12" t="n">
+        <v>357</v>
+      </c>
+      <c r="K12" t="n">
         <v>356</v>
       </c>
-      <c r="K12" t="n">
-        <v>355</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.001450684628675147</v>
+        <v>0.001063991465749536</v>
       </c>
       <c r="M12" t="n">
-        <v>2.619298637709231</v>
+        <v>2.624233694150323</v>
       </c>
       <c r="N12" t="n">
-        <v>10.72498799885564</v>
+        <v>10.74596247606132</v>
       </c>
       <c r="O12" t="n">
-        <v>3.274902746472885</v>
+        <v>3.278103487698539</v>
       </c>
       <c r="P12" t="n">
-        <v>391.6300187881938</v>
+        <v>391.6563623210823</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22303,28 +22361,28 @@
         <v>0.0634</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1063126576626575</v>
+        <v>-0.1082133759083937</v>
       </c>
       <c r="J13" t="n">
+        <v>357</v>
+      </c>
+      <c r="K13" t="n">
         <v>356</v>
       </c>
-      <c r="K13" t="n">
-        <v>355</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.05770106465668479</v>
+        <v>0.05984295695183672</v>
       </c>
       <c r="M13" t="n">
-        <v>2.524496660229818</v>
+        <v>2.526298226204637</v>
       </c>
       <c r="N13" t="n">
-        <v>9.730477281809806</v>
+        <v>9.73308525165328</v>
       </c>
       <c r="O13" t="n">
-        <v>3.11937129592003</v>
+        <v>3.119789296034795</v>
       </c>
       <c r="P13" t="n">
-        <v>398.1662392159692</v>
+        <v>398.1864039015559</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22366,7 +22424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N357"/>
+  <dimension ref="A1:N358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48049,6 +48107,78 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-35.257124741108406,174.13146165037662</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-35.25777006825775,174.1317420736326</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-35.25829147723293,174.13229720570948</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-35.25877675428566,174.13292647562875</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-35.259225097577996,174.13361650703857</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-35.25956996536592,174.1343767190497</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-35.259895950518356,174.1351577147421</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-35.26015100050194,174.1359989357167</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-35.26032684907894,174.13686185772025</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-35.260529530824776,174.1377061678744</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-35.260606827413675,174.1386173034286</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-35.260817713448596,174.13948688500946</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0064/nzd0064.xlsx
+++ b/data/nzd0064/nzd0064.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N358"/>
+  <dimension ref="A1:N360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17624,6 +17624,102 @@
       <c r="N358" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>384.14</v>
+      </c>
+      <c r="C359" t="n">
+        <v>380.34</v>
+      </c>
+      <c r="D359" t="n">
+        <v>385.08</v>
+      </c>
+      <c r="E359" t="n">
+        <v>382.92</v>
+      </c>
+      <c r="F359" t="n">
+        <v>379.1</v>
+      </c>
+      <c r="G359" t="n">
+        <v>382.7</v>
+      </c>
+      <c r="H359" t="n">
+        <v>376.23</v>
+      </c>
+      <c r="I359" t="n">
+        <v>372.79</v>
+      </c>
+      <c r="J359" t="n">
+        <v>379.52</v>
+      </c>
+      <c r="K359" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="L359" t="n">
+        <v>383.77</v>
+      </c>
+      <c r="M359" t="n">
+        <v>393.31</v>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>383.49</v>
+      </c>
+      <c r="C360" t="n">
+        <v>380.47</v>
+      </c>
+      <c r="D360" t="n">
+        <v>383.71</v>
+      </c>
+      <c r="E360" t="n">
+        <v>382.41</v>
+      </c>
+      <c r="F360" t="n">
+        <v>378.96</v>
+      </c>
+      <c r="G360" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="H360" t="n">
+        <v>376.08</v>
+      </c>
+      <c r="I360" t="n">
+        <v>372.16</v>
+      </c>
+      <c r="J360" t="n">
+        <v>379.52</v>
+      </c>
+      <c r="K360" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="L360" t="n">
+        <v>383.77</v>
+      </c>
+      <c r="M360" t="n">
+        <v>393.3</v>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B365"/>
+  <dimension ref="A1:B367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21291,6 +21387,26 @@
       </c>
       <c r="B365" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>
@@ -21459,28 +21575,28 @@
         <v>0.0688</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.003799454096751423</v>
+        <v>-0.003102289243843053</v>
       </c>
       <c r="J2" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K2" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L2" t="n">
-        <v>7.583951039091819e-05</v>
+        <v>5.120210883102772e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.287536598383334</v>
+        <v>2.278029502389466</v>
       </c>
       <c r="N2" t="n">
-        <v>9.978879002585526</v>
+        <v>9.925253811360893</v>
       </c>
       <c r="O2" t="n">
-        <v>3.158936372038146</v>
+        <v>3.150437082590429</v>
       </c>
       <c r="P2" t="n">
-        <v>383.3175967073383</v>
+        <v>383.3101009383294</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21541,28 +21657,28 @@
         <v>0.1268</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02990250498461781</v>
+        <v>0.02629314076851786</v>
       </c>
       <c r="J3" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K3" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006064327258981095</v>
+        <v>0.004722370844672419</v>
       </c>
       <c r="M3" t="n">
-        <v>2.026155429966222</v>
+        <v>2.032408230442564</v>
       </c>
       <c r="N3" t="n">
-        <v>7.790179808126085</v>
+        <v>7.801022940072134</v>
       </c>
       <c r="O3" t="n">
-        <v>2.791089358678092</v>
+        <v>2.793031138400024</v>
       </c>
       <c r="P3" t="n">
-        <v>382.7597469232269</v>
+        <v>382.7980956157132</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21623,28 +21739,28 @@
         <v>0.1164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02311986269946526</v>
+        <v>0.01891653889755981</v>
       </c>
       <c r="J4" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K4" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003468645249913194</v>
+        <v>0.002332745761686517</v>
       </c>
       <c r="M4" t="n">
-        <v>2.129125583650952</v>
+        <v>2.137972728249833</v>
       </c>
       <c r="N4" t="n">
-        <v>8.163159357508325</v>
+        <v>8.193776860110377</v>
       </c>
       <c r="O4" t="n">
-        <v>2.857124316075226</v>
+        <v>2.862477399056694</v>
       </c>
       <c r="P4" t="n">
-        <v>387.4500858829624</v>
+        <v>387.4947537350771</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21705,28 +21821,28 @@
         <v>0.1182</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07247215127995721</v>
+        <v>-0.07281604068943387</v>
       </c>
       <c r="J5" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02810185677084787</v>
+        <v>0.02871357289484699</v>
       </c>
       <c r="M5" t="n">
-        <v>2.424161687131467</v>
+        <v>2.412366717183699</v>
       </c>
       <c r="N5" t="n">
-        <v>9.655721564282736</v>
+        <v>9.602773244856936</v>
       </c>
       <c r="O5" t="n">
-        <v>3.107365695292837</v>
+        <v>3.098834175114399</v>
       </c>
       <c r="P5" t="n">
-        <v>384.8886423976508</v>
+        <v>384.8922990069091</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21787,28 +21903,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03646299029492616</v>
+        <v>-0.04060739661681934</v>
       </c>
       <c r="J6" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K6" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008998144175488387</v>
+        <v>0.01117537837658444</v>
       </c>
       <c r="M6" t="n">
-        <v>2.103006408447279</v>
+        <v>2.111178104733655</v>
       </c>
       <c r="N6" t="n">
-        <v>7.783640603326271</v>
+        <v>7.811776300394996</v>
       </c>
       <c r="O6" t="n">
-        <v>2.789917669632255</v>
+        <v>2.794955509555563</v>
       </c>
       <c r="P6" t="n">
-        <v>383.6140086019662</v>
+        <v>383.6580436314553</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21869,28 +21985,28 @@
         <v>0.1432</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06871008939515946</v>
+        <v>0.06685891782132031</v>
       </c>
       <c r="J7" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K7" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02463025877187919</v>
+        <v>0.02361158636237881</v>
       </c>
       <c r="M7" t="n">
-        <v>2.514673296624768</v>
+        <v>2.509277406153741</v>
       </c>
       <c r="N7" t="n">
-        <v>9.937977789427306</v>
+        <v>9.896886841390362</v>
       </c>
       <c r="O7" t="n">
-        <v>3.152455834651345</v>
+        <v>3.145931792234276</v>
       </c>
       <c r="P7" t="n">
-        <v>382.4427651211862</v>
+        <v>382.4624343688672</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -21951,28 +22067,28 @@
         <v>0.1037</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01217302430484212</v>
+        <v>0.008677138836185002</v>
       </c>
       <c r="J8" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K8" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0008868535906283448</v>
+        <v>0.0004539949212863936</v>
       </c>
       <c r="M8" t="n">
-        <v>2.295079556413471</v>
+        <v>2.29644375953887</v>
       </c>
       <c r="N8" t="n">
-        <v>8.873938488068022</v>
+        <v>8.875388126423839</v>
       </c>
       <c r="O8" t="n">
-        <v>2.978915656420642</v>
+        <v>2.979158962932968</v>
       </c>
       <c r="P8" t="n">
-        <v>378.8800153359678</v>
+        <v>378.917159934884</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22033,28 +22149,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03830666279774955</v>
+        <v>0.03807842471835392</v>
       </c>
       <c r="J9" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K9" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007356741902165509</v>
+        <v>0.007362280270864607</v>
       </c>
       <c r="M9" t="n">
-        <v>2.529815598208961</v>
+        <v>2.517440298689156</v>
       </c>
       <c r="N9" t="n">
-        <v>10.52477949688652</v>
+        <v>10.46691851619144</v>
       </c>
       <c r="O9" t="n">
-        <v>3.244191655387598</v>
+        <v>3.235261738436543</v>
       </c>
       <c r="P9" t="n">
-        <v>371.6537334910472</v>
+        <v>371.656162020291</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22115,28 +22231,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01442681245049056</v>
+        <v>0.007944874475888517</v>
       </c>
       <c r="J10" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K10" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001475569230383389</v>
+        <v>0.0004433150068429148</v>
       </c>
       <c r="M10" t="n">
-        <v>2.126781710553783</v>
+        <v>2.148228056900319</v>
       </c>
       <c r="N10" t="n">
-        <v>7.486805790767458</v>
+        <v>7.619939853611716</v>
       </c>
       <c r="O10" t="n">
-        <v>2.73620280512382</v>
+        <v>2.760423853978174</v>
       </c>
       <c r="P10" t="n">
-        <v>384.791524905059</v>
+        <v>384.8603953947787</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22197,28 +22313,28 @@
         <v>0.1052</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09804174168260034</v>
+        <v>0.09144501471294784</v>
       </c>
       <c r="J11" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K11" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04032323564911677</v>
+        <v>0.03519371515494585</v>
       </c>
       <c r="M11" t="n">
-        <v>2.627996570449004</v>
+        <v>2.637254454058011</v>
       </c>
       <c r="N11" t="n">
-        <v>12.16041320789328</v>
+        <v>12.27375770576939</v>
       </c>
       <c r="O11" t="n">
-        <v>3.487178402074274</v>
+        <v>3.503392313996449</v>
       </c>
       <c r="P11" t="n">
-        <v>377.2696500351551</v>
+        <v>377.3397401763741</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22279,28 +22395,28 @@
         <v>0.056</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01470863123172406</v>
+        <v>0.005182358150367715</v>
       </c>
       <c r="J12" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K12" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001063991465749536</v>
+        <v>0.000129366888236615</v>
       </c>
       <c r="M12" t="n">
-        <v>2.624233694150323</v>
+        <v>2.657542313626128</v>
       </c>
       <c r="N12" t="n">
-        <v>10.74596247606132</v>
+        <v>11.06124199239033</v>
       </c>
       <c r="O12" t="n">
-        <v>3.278103487698539</v>
+        <v>3.325844553251148</v>
       </c>
       <c r="P12" t="n">
-        <v>391.6563623210823</v>
+        <v>391.757975717284</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22361,28 +22477,28 @@
         <v>0.0634</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1082133759083937</v>
+        <v>-0.1105323132957304</v>
       </c>
       <c r="J13" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K13" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05984295695183672</v>
+        <v>0.06289021671821415</v>
       </c>
       <c r="M13" t="n">
-        <v>2.526298226204637</v>
+        <v>2.522864044869829</v>
       </c>
       <c r="N13" t="n">
-        <v>9.73308525165328</v>
+        <v>9.700949964595596</v>
       </c>
       <c r="O13" t="n">
-        <v>3.119789296034795</v>
+        <v>3.114634804370425</v>
       </c>
       <c r="P13" t="n">
-        <v>398.1864039015559</v>
+        <v>398.2111391970584</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22424,7 +22540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N358"/>
+  <dimension ref="A1:N360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48179,6 +48295,150 @@
         </is>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-35.257118610491844,174.13148056173782</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-35.25776980053169,174.13174264670903</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-35.258293643827685,174.1322944086658</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-35.25877224053779,174.13293085804423</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-35.259229603624995,174.13361285791802</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-35.25957077528261,174.13437623612853</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-35.25988714483398,174.13516131006065</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-35.26012111816873,174.13601163510117</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-35.26034816941728,174.13685364426894</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-35.260555036527926,174.13769915636297</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-35.26064174204308,174.13860504310696</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-35.26080723825208,174.1394913225749</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-35.25712076449258,174.13147391720585</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-35.25776922045857,174.13174388837456</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-35.258302124498016,174.13228346023615</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-35.25877583743063,174.13292736580692</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-35.25923065503594,174.1336120064565</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-35.259571585199275,174.13437575320737</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-35.259888427215216,174.1351607864706</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-35.26012648166454,174.13600935572512</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-35.26034816941728,174.13685364426894</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-35.260555036527926,174.13769915636297</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-35.26064174204308,174.13860504310696</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-35.26080732341628,174.13949128649713</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0064/nzd0064.xlsx
+++ b/data/nzd0064/nzd0064.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N360"/>
+  <dimension ref="A1:N362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17720,6 +17720,102 @@
       <c r="N360" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>381.01</v>
+      </c>
+      <c r="C361" t="n">
+        <v>380.22</v>
+      </c>
+      <c r="D361" t="n">
+        <v>382.85</v>
+      </c>
+      <c r="E361" t="n">
+        <v>380.87</v>
+      </c>
+      <c r="F361" t="n">
+        <v>377.67</v>
+      </c>
+      <c r="G361" t="n">
+        <v>380.57</v>
+      </c>
+      <c r="H361" t="n">
+        <v>374.41</v>
+      </c>
+      <c r="I361" t="n">
+        <v>370.27</v>
+      </c>
+      <c r="J361" t="n">
+        <v>376.35</v>
+      </c>
+      <c r="K361" t="n">
+        <v>371.08</v>
+      </c>
+      <c r="L361" t="n">
+        <v>378.65</v>
+      </c>
+      <c r="M361" t="n">
+        <v>390.31</v>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>377.89</v>
+      </c>
+      <c r="C362" t="n">
+        <v>377.86</v>
+      </c>
+      <c r="D362" t="n">
+        <v>381.65</v>
+      </c>
+      <c r="E362" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="F362" t="n">
+        <v>377.13</v>
+      </c>
+      <c r="G362" t="n">
+        <v>379.06</v>
+      </c>
+      <c r="H362" t="n">
+        <v>375.23</v>
+      </c>
+      <c r="I362" t="n">
+        <v>370.15</v>
+      </c>
+      <c r="J362" t="n">
+        <v>376.35</v>
+      </c>
+      <c r="K362" t="n">
+        <v>371.08</v>
+      </c>
+      <c r="L362" t="n">
+        <v>378.65</v>
+      </c>
+      <c r="M362" t="n">
+        <v>390.31</v>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B367"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21407,6 +21503,26 @@
       </c>
       <c r="B367" t="n">
         <v>0.91</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>
@@ -21575,28 +21691,28 @@
         <v>0.0688</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.003102289243843053</v>
+        <v>-0.007502610486570513</v>
       </c>
       <c r="J2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K2" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L2" t="n">
-        <v>5.120210883102772e-05</v>
+        <v>0.0003005034615981561</v>
       </c>
       <c r="M2" t="n">
-        <v>2.278029502389466</v>
+        <v>2.28634719077109</v>
       </c>
       <c r="N2" t="n">
-        <v>9.925253811360893</v>
+        <v>9.961883968426504</v>
       </c>
       <c r="O2" t="n">
-        <v>3.150437082590429</v>
+        <v>3.15624523261842</v>
       </c>
       <c r="P2" t="n">
-        <v>383.3101009383294</v>
+        <v>383.3578435201163</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21657,28 +21773,28 @@
         <v>0.1268</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02629314076851786</v>
+        <v>0.02117847201882138</v>
       </c>
       <c r="J3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004722370844672419</v>
+        <v>0.003063194096426192</v>
       </c>
       <c r="M3" t="n">
-        <v>2.032408230442564</v>
+        <v>2.04632933003385</v>
       </c>
       <c r="N3" t="n">
-        <v>7.801022940072134</v>
+        <v>7.873702400068766</v>
       </c>
       <c r="O3" t="n">
-        <v>2.793031138400024</v>
+        <v>2.806011831776332</v>
       </c>
       <c r="P3" t="n">
-        <v>382.7980956157132</v>
+        <v>382.8529059842703</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21739,28 +21855,28 @@
         <v>0.1164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01891653889755981</v>
+        <v>0.01232277053203431</v>
       </c>
       <c r="J4" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K4" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002332745761686517</v>
+        <v>0.000982271205764218</v>
       </c>
       <c r="M4" t="n">
-        <v>2.137972728249833</v>
+        <v>2.158567782794751</v>
       </c>
       <c r="N4" t="n">
-        <v>8.193776860110377</v>
+        <v>8.330194465331221</v>
       </c>
       <c r="O4" t="n">
-        <v>2.862477399056694</v>
+        <v>2.886207626857642</v>
       </c>
       <c r="P4" t="n">
-        <v>387.4947537350771</v>
+        <v>387.5654095840524</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21821,28 +21937,28 @@
         <v>0.1182</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07281604068943387</v>
+        <v>-0.07570734675771142</v>
       </c>
       <c r="J5" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K5" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02871357289484699</v>
+        <v>0.03124533144963659</v>
       </c>
       <c r="M5" t="n">
-        <v>2.412366717183699</v>
+        <v>2.41307814975108</v>
       </c>
       <c r="N5" t="n">
-        <v>9.602773244856936</v>
+        <v>9.585203991953883</v>
       </c>
       <c r="O5" t="n">
-        <v>3.098834175114399</v>
+        <v>3.095998060715459</v>
       </c>
       <c r="P5" t="n">
-        <v>384.8922990069091</v>
+        <v>384.9232818852273</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21903,28 +22019,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04060739661681934</v>
+        <v>-0.04654073362599565</v>
       </c>
       <c r="J6" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K6" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01117537837658444</v>
+        <v>0.01454706244354675</v>
       </c>
       <c r="M6" t="n">
-        <v>2.111178104733655</v>
+        <v>2.128159407150379</v>
       </c>
       <c r="N6" t="n">
-        <v>7.811776300394996</v>
+        <v>7.914503404729635</v>
       </c>
       <c r="O6" t="n">
-        <v>2.794955509555563</v>
+        <v>2.813272721356682</v>
       </c>
       <c r="P6" t="n">
-        <v>383.6580436314553</v>
+        <v>383.7216211220627</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21985,28 +22101,28 @@
         <v>0.1432</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06685891782132031</v>
+        <v>0.06177966247206875</v>
       </c>
       <c r="J7" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K7" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02361158636237881</v>
+        <v>0.02026702310043105</v>
       </c>
       <c r="M7" t="n">
-        <v>2.509277406153741</v>
+        <v>2.518892256874443</v>
       </c>
       <c r="N7" t="n">
-        <v>9.896886841390362</v>
+        <v>9.951887580166323</v>
       </c>
       <c r="O7" t="n">
-        <v>3.145931792234276</v>
+        <v>3.154661246499586</v>
       </c>
       <c r="P7" t="n">
-        <v>382.4624343688672</v>
+        <v>382.516862955576</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -22067,28 +22183,28 @@
         <v>0.1037</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008677138836185002</v>
+        <v>0.003714254452144669</v>
       </c>
       <c r="J8" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K8" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004539949212863936</v>
+        <v>8.332933783805618e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.29644375953887</v>
+        <v>2.30360341180085</v>
       </c>
       <c r="N8" t="n">
-        <v>8.875388126423839</v>
+        <v>8.929061590838286</v>
       </c>
       <c r="O8" t="n">
-        <v>2.979158962932968</v>
+        <v>2.988153542045369</v>
       </c>
       <c r="P8" t="n">
-        <v>378.917159934884</v>
+        <v>378.9703352441092</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22149,28 +22265,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03807842471835392</v>
+        <v>0.03525244244820289</v>
       </c>
       <c r="J9" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K9" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007362280270864607</v>
+        <v>0.006378422296677844</v>
       </c>
       <c r="M9" t="n">
-        <v>2.517440298689156</v>
+        <v>2.516359231379541</v>
       </c>
       <c r="N9" t="n">
-        <v>10.46691851619144</v>
+        <v>10.44197874043891</v>
       </c>
       <c r="O9" t="n">
-        <v>3.235261738436543</v>
+        <v>3.231405072168902</v>
       </c>
       <c r="P9" t="n">
-        <v>371.656162020291</v>
+        <v>371.6864428785871</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22231,28 +22347,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.007944874475888517</v>
+        <v>-0.002060083322391238</v>
       </c>
       <c r="J10" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K10" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0004433150068429148</v>
+        <v>2.864257289070249e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.148228056900319</v>
+        <v>2.189346147341622</v>
       </c>
       <c r="N10" t="n">
-        <v>7.619939853611716</v>
+        <v>7.991747268480857</v>
       </c>
       <c r="O10" t="n">
-        <v>2.760423853978174</v>
+        <v>2.82696785770211</v>
       </c>
       <c r="P10" t="n">
-        <v>384.8603953947787</v>
+        <v>384.967599032552</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22313,28 +22429,28 @@
         <v>0.1052</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09144501471294784</v>
+        <v>0.08146336461501251</v>
       </c>
       <c r="J11" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K11" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03519371515494585</v>
+        <v>0.02758589185992433</v>
       </c>
       <c r="M11" t="n">
-        <v>2.637254454058011</v>
+        <v>2.660118927327551</v>
       </c>
       <c r="N11" t="n">
-        <v>12.27375770576939</v>
+        <v>12.61785533353106</v>
       </c>
       <c r="O11" t="n">
-        <v>3.503392313996449</v>
+        <v>3.552162064648946</v>
       </c>
       <c r="P11" t="n">
-        <v>377.3397401763741</v>
+        <v>377.4466940759093</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22395,28 +22511,28 @@
         <v>0.056</v>
       </c>
       <c r="I12" t="n">
-        <v>0.005182358150367715</v>
+        <v>-0.01007845734748913</v>
       </c>
       <c r="J12" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K12" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000129366888236615</v>
+        <v>0.0004558377076239184</v>
       </c>
       <c r="M12" t="n">
-        <v>2.657542313626128</v>
+        <v>2.721259944880834</v>
       </c>
       <c r="N12" t="n">
-        <v>11.06124199239033</v>
+        <v>11.95705549650151</v>
       </c>
       <c r="O12" t="n">
-        <v>3.325844553251148</v>
+        <v>3.457897554367612</v>
       </c>
       <c r="P12" t="n">
-        <v>391.757975717284</v>
+        <v>391.9221337411136</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22477,28 +22593,28 @@
         <v>0.0634</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1105323132957304</v>
+        <v>-0.1162371853968463</v>
       </c>
       <c r="J13" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K13" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06289021671821415</v>
+        <v>0.06903839134593037</v>
       </c>
       <c r="M13" t="n">
-        <v>2.522864044869829</v>
+        <v>2.534417032084037</v>
       </c>
       <c r="N13" t="n">
-        <v>9.700949964595596</v>
+        <v>9.780828868250696</v>
       </c>
       <c r="O13" t="n">
-        <v>3.114634804370425</v>
+        <v>3.127431672834867</v>
       </c>
       <c r="P13" t="n">
-        <v>398.2111391970584</v>
+        <v>398.2725055393556</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22540,7 +22656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N360"/>
+  <dimension ref="A1:N362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48439,6 +48555,150 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-35.257128982830594,174.13144856575747</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-35.25777033598381,174.13174150055622</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-35.25830744812999,174.13227658749815</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-35.258786698635866,174.13291682061796</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-35.25924034303656,174.13360416084583</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-35.25958802650741,174.13436594990534</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-35.2599027043927,174.13515495716715</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-35.260142572151686,174.13600251759527</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-35.26037542162313,174.13684314561746</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-35.260581685589756,174.13769183053796</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-35.260686100081664,174.13858946670356</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-35.26083278751163,174.13948049924258</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-35.25713932202259,174.13141667199233</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-35.25778086653979,174.1317189595479</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-35.25831487645304,174.13226699762964</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-35.258792905038476,174.1329107947944</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-35.259244398478536,174.13360087663617</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-35.259600256248426,174.13435865779147</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-35.25989569404212,174.13515781946012</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-35.2601435937699,174.13600208342822</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-35.26037542162313,174.13684314561746</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-35.260581685589756,174.13769183053796</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-35.260686100081664,174.13858946670356</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-35.26083278751163,174.13948049924258</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0064/nzd0064.xlsx
+++ b/data/nzd0064/nzd0064.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N362"/>
+  <dimension ref="A1:N365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17814,6 +17814,150 @@
         <v>390.31</v>
       </c>
       <c r="N362" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>375.16</v>
+      </c>
+      <c r="C363" t="n">
+        <v>375.45</v>
+      </c>
+      <c r="D363" t="n">
+        <v>380.05</v>
+      </c>
+      <c r="E363" t="n">
+        <v>377.91</v>
+      </c>
+      <c r="F363" t="n">
+        <v>374.71</v>
+      </c>
+      <c r="G363" t="n">
+        <v>376.87</v>
+      </c>
+      <c r="H363" t="n">
+        <v>372.99</v>
+      </c>
+      <c r="I363" t="n">
+        <v>367.95</v>
+      </c>
+      <c r="J363" t="n">
+        <v>372.7</v>
+      </c>
+      <c r="K363" t="n">
+        <v>367.54</v>
+      </c>
+      <c r="L363" t="n">
+        <v>374.44</v>
+      </c>
+      <c r="M363" t="n">
+        <v>387.02</v>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>374.16</v>
+      </c>
+      <c r="C364" t="n">
+        <v>376.47</v>
+      </c>
+      <c r="D364" t="n">
+        <v>380.68</v>
+      </c>
+      <c r="E364" t="n">
+        <v>379.06</v>
+      </c>
+      <c r="F364" t="n">
+        <v>376.47</v>
+      </c>
+      <c r="G364" t="n">
+        <v>378.47</v>
+      </c>
+      <c r="H364" t="n">
+        <v>374.14</v>
+      </c>
+      <c r="I364" t="n">
+        <v>369.05</v>
+      </c>
+      <c r="J364" t="n">
+        <v>376.02</v>
+      </c>
+      <c r="K364" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="L364" t="n">
+        <v>377.83</v>
+      </c>
+      <c r="M364" t="n">
+        <v>388.13</v>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>375.58</v>
+      </c>
+      <c r="C365" t="n">
+        <v>377.78</v>
+      </c>
+      <c r="D365" t="n">
+        <v>382.31</v>
+      </c>
+      <c r="E365" t="n">
+        <v>380.36</v>
+      </c>
+      <c r="F365" t="n">
+        <v>377.92</v>
+      </c>
+      <c r="G365" t="n">
+        <v>379.26</v>
+      </c>
+      <c r="H365" t="n">
+        <v>376.04</v>
+      </c>
+      <c r="I365" t="n">
+        <v>369.84</v>
+      </c>
+      <c r="J365" t="n">
+        <v>378.39</v>
+      </c>
+      <c r="K365" t="n">
+        <v>371.23</v>
+      </c>
+      <c r="L365" t="n">
+        <v>379.91</v>
+      </c>
+      <c r="M365" t="n">
+        <v>389.15</v>
+      </c>
+      <c r="N365" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17830,7 +17974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21523,6 +21667,36 @@
       </c>
       <c r="B369" t="n">
         <v>-0.01</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -21691,28 +21865,28 @@
         <v>0.0688</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.007502610486570513</v>
+        <v>-0.02150144314563095</v>
       </c>
       <c r="J2" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K2" t="n">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003005034615981561</v>
+        <v>0.002379036287237124</v>
       </c>
       <c r="M2" t="n">
-        <v>2.28634719077109</v>
+        <v>2.336302322496836</v>
       </c>
       <c r="N2" t="n">
-        <v>9.961883968426504</v>
+        <v>10.42556324947163</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15624523261842</v>
+        <v>3.228864080365049</v>
       </c>
       <c r="P2" t="n">
-        <v>383.3578435201163</v>
+        <v>383.5101626674499</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21773,28 +21947,28 @@
         <v>0.1268</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02117847201882138</v>
+        <v>0.009635879334262356</v>
       </c>
       <c r="J3" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K3" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003063194096426192</v>
+        <v>0.0006175810587057962</v>
       </c>
       <c r="M3" t="n">
-        <v>2.04632933003385</v>
+        <v>2.08766173985044</v>
       </c>
       <c r="N3" t="n">
-        <v>7.873702400068766</v>
+        <v>8.192712563551947</v>
       </c>
       <c r="O3" t="n">
-        <v>2.806011831776332</v>
+        <v>2.86229148822267</v>
       </c>
       <c r="P3" t="n">
-        <v>382.8529059842703</v>
+        <v>382.9769532428779</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21855,28 +22029,28 @@
         <v>0.1164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01232277053203431</v>
+        <v>0.0007314828866350804</v>
       </c>
       <c r="J4" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K4" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000982271205764218</v>
+        <v>3.373385978888699e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>2.158567782794751</v>
+        <v>2.198578047467225</v>
       </c>
       <c r="N4" t="n">
-        <v>8.330194465331221</v>
+        <v>8.648645867806573</v>
       </c>
       <c r="O4" t="n">
-        <v>2.886207626857642</v>
+        <v>2.940858015580925</v>
       </c>
       <c r="P4" t="n">
-        <v>387.5654095840524</v>
+        <v>387.6899805649095</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21937,28 +22111,28 @@
         <v>0.1182</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07570734675771142</v>
+        <v>-0.08208469743429424</v>
       </c>
       <c r="J5" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K5" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03124533144963659</v>
+        <v>0.03675084441318821</v>
       </c>
       <c r="M5" t="n">
-        <v>2.41307814975108</v>
+        <v>2.424308104053474</v>
       </c>
       <c r="N5" t="n">
-        <v>9.585203991953883</v>
+        <v>9.62948349564536</v>
       </c>
       <c r="O5" t="n">
-        <v>3.095998060715459</v>
+        <v>3.103140908119604</v>
       </c>
       <c r="P5" t="n">
-        <v>384.9232818852273</v>
+        <v>384.9918123860869</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -22019,28 +22193,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04654073362599565</v>
+        <v>-0.05683312333029564</v>
       </c>
       <c r="J6" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K6" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01454706244354675</v>
+        <v>0.02111998809031879</v>
       </c>
       <c r="M6" t="n">
-        <v>2.128159407150379</v>
+        <v>2.161837088512369</v>
       </c>
       <c r="N6" t="n">
-        <v>7.914503404729635</v>
+        <v>8.162930789567371</v>
       </c>
       <c r="O6" t="n">
-        <v>2.813272721356682</v>
+        <v>2.857084316145985</v>
       </c>
       <c r="P6" t="n">
-        <v>383.7216211220627</v>
+        <v>383.8322263718463</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -22101,28 +22275,28 @@
         <v>0.1432</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06177966247206875</v>
+        <v>0.05171836027737989</v>
       </c>
       <c r="J7" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K7" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02026702310043105</v>
+        <v>0.01414635332302894</v>
       </c>
       <c r="M7" t="n">
-        <v>2.518892256874443</v>
+        <v>2.5464521180356</v>
       </c>
       <c r="N7" t="n">
-        <v>9.951887580166323</v>
+        <v>10.16400138658547</v>
       </c>
       <c r="O7" t="n">
-        <v>3.154661246499586</v>
+        <v>3.188103101624141</v>
       </c>
       <c r="P7" t="n">
-        <v>382.516862955576</v>
+        <v>382.6249889937281</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -22183,28 +22357,28 @@
         <v>0.1037</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003714254452144669</v>
+        <v>-0.004167252355308881</v>
       </c>
       <c r="J8" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K8" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L8" t="n">
-        <v>8.332933783805618e-05</v>
+        <v>0.0001046879830489678</v>
       </c>
       <c r="M8" t="n">
-        <v>2.30360341180085</v>
+        <v>2.316797233606037</v>
       </c>
       <c r="N8" t="n">
-        <v>8.929061590838286</v>
+        <v>9.044083762916298</v>
       </c>
       <c r="O8" t="n">
-        <v>2.988153542045369</v>
+        <v>3.007338318665909</v>
       </c>
       <c r="P8" t="n">
-        <v>378.9703352441092</v>
+        <v>379.0550292346857</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22265,28 +22439,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03525244244820289</v>
+        <v>0.0290437046347843</v>
       </c>
       <c r="J9" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K9" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006378422296677844</v>
+        <v>0.004373895764342106</v>
       </c>
       <c r="M9" t="n">
-        <v>2.516359231379541</v>
+        <v>2.524025160540907</v>
       </c>
       <c r="N9" t="n">
-        <v>10.44197874043891</v>
+        <v>10.46981827523063</v>
       </c>
       <c r="O9" t="n">
-        <v>3.231405072168902</v>
+        <v>3.235709856465909</v>
       </c>
       <c r="P9" t="n">
-        <v>371.6864428785871</v>
+        <v>371.7531641973326</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22347,28 +22521,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.002060083322391238</v>
+        <v>-0.01757348234371699</v>
       </c>
       <c r="J10" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K10" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L10" t="n">
-        <v>2.864257289070249e-05</v>
+        <v>0.001942719862172315</v>
       </c>
       <c r="M10" t="n">
-        <v>2.189346147341622</v>
+        <v>2.257215743560324</v>
       </c>
       <c r="N10" t="n">
-        <v>7.991747268480857</v>
+        <v>8.651038010632321</v>
       </c>
       <c r="O10" t="n">
-        <v>2.82696785770211</v>
+        <v>2.941264695778386</v>
       </c>
       <c r="P10" t="n">
-        <v>384.967599032552</v>
+        <v>385.1343063493097</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22429,28 +22603,28 @@
         <v>0.1052</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08146336461501251</v>
+        <v>0.06432375090314833</v>
       </c>
       <c r="J11" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K11" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02758589185992433</v>
+        <v>0.01660291390603341</v>
       </c>
       <c r="M11" t="n">
-        <v>2.660118927327551</v>
+        <v>2.706155228805182</v>
       </c>
       <c r="N11" t="n">
-        <v>12.61785533353106</v>
+        <v>13.36271171293753</v>
       </c>
       <c r="O11" t="n">
-        <v>3.552162064648946</v>
+        <v>3.655504303504173</v>
       </c>
       <c r="P11" t="n">
-        <v>377.4466940759093</v>
+        <v>377.6308907543247</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22511,28 +22685,28 @@
         <v>0.056</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01007845734748913</v>
+        <v>-0.03420466599055236</v>
       </c>
       <c r="J12" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K12" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0004558377076239184</v>
+        <v>0.004669188857615914</v>
       </c>
       <c r="M12" t="n">
-        <v>2.721259944880834</v>
+        <v>2.8239607649624</v>
       </c>
       <c r="N12" t="n">
-        <v>11.95705549650151</v>
+        <v>13.53487541843129</v>
       </c>
       <c r="O12" t="n">
-        <v>3.457897554367612</v>
+        <v>3.678977496320314</v>
       </c>
       <c r="P12" t="n">
-        <v>391.9221337411136</v>
+        <v>392.1824215329585</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22593,28 +22767,28 @@
         <v>0.0634</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1162371853968463</v>
+        <v>-0.1281800339372439</v>
       </c>
       <c r="J13" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K13" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06903839134593037</v>
+        <v>0.08107125751712596</v>
       </c>
       <c r="M13" t="n">
-        <v>2.534417032084037</v>
+        <v>2.567444029221052</v>
       </c>
       <c r="N13" t="n">
-        <v>9.780828868250696</v>
+        <v>10.10678990423702</v>
       </c>
       <c r="O13" t="n">
-        <v>3.127431672834867</v>
+        <v>3.179117787097078</v>
       </c>
       <c r="P13" t="n">
-        <v>398.2725055393556</v>
+        <v>398.4013551458696</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22656,7 +22830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N362"/>
+  <dimension ref="A1:N365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48699,6 +48873,222 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>-35.25714836880883,174.13138876494108</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>-35.257791620196556,174.13169594096976</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>-35.258324780882646,174.1322542111356</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-35.258807574716194,174.13289655193518</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-35.2592625728656,174.13358615850734</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-35.259617993421756,174.1343480818079</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-35.25991484426796,174.1351500005123</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-35.26016232343699,174.13599412369686</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-35.260406800344846,174.13683105725642</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-35.2606128201366,174.1376832716475</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-35.260722574170465,174.13857665875022</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-35.260860806531845,174.1394686296472</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>-35.257151682648335,174.13137854257639</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>-35.257787068856864,174.1317056832733</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>-35.25832088101364,174.132259245818</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-35.25879946407728,174.13290442659357</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-35.25924935512972,174.13359686260168</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-35.25960503475641,174.13435580855432</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-35.25990501267886,174.13515401470474</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-35.2601529586035,174.135998103563</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-35.2603782586035,174.13684205269752</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-35.26059470229302,174.1376882522455</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-35.26069320429858,174.13858697204367</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>-35.26085135330629,174.13947263428363</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>-35.25714697699596,174.131393058334</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>-35.25778122350771,174.13171819544584</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>-35.25831079087546,174.13227227205752</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-35.25879029552832,174.13291332837943</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-35.2592384655171,174.13360568131318</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-35.25959863641522,174.13435962363448</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-35.25988876918353,174.1351606468466</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-35.26014623295029,174.13600096182992</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-35.2603578839261,174.1368499018482</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-35.260580366329265,174.13769219320267</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-35.2606751838458,174.1385932999606</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>-35.260842666558396,174.13947631421897</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
